--- a/excel/数据分析.xlsx
+++ b/excel/数据分析.xlsx
@@ -4,18 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="90" windowWidth="28035" windowHeight="12345" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="90" windowWidth="28035" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="数据透析分析" sheetId="5" r:id="rId1"/>
     <sheet name="第一学期成绩" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -743,7 +741,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="英语成绩">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="英语成绩">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0"/>
@@ -1971,24 +1969,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>